--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/SpawnList.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/SpawnList.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="75">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -29,10 +29,13 @@
     <t xml:space="preserve">all</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.338 Patch 2</t>
+    <t xml:space="preserve">EA 23.352</t>
   </si>
   <si>
     <t xml:space="preserve">chara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_statue</t>
   </si>
   <si>
     <t xml:space="preserve">c_guest</t>
@@ -317,7 +320,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3"/>
     </row>
@@ -326,7 +329,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4"/>
     </row>
@@ -335,7 +338,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C5"/>
     </row>
@@ -389,7 +392,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11"/>
     </row>
@@ -398,7 +401,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12"/>
     </row>
@@ -407,7 +410,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13"/>
     </row>
@@ -416,7 +419,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14"/>
     </row>
@@ -425,7 +428,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15"/>
     </row>
@@ -443,7 +446,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C17"/>
     </row>
@@ -452,7 +455,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C18"/>
     </row>
@@ -470,7 +473,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C20"/>
     </row>
@@ -479,7 +482,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C21"/>
     </row>
@@ -497,7 +500,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C23"/>
     </row>
@@ -506,7 +509,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24"/>
     </row>
@@ -515,7 +518,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C25"/>
     </row>
@@ -524,7 +527,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26"/>
     </row>
@@ -533,7 +536,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C27"/>
     </row>
@@ -542,7 +545,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28"/>
     </row>
@@ -551,7 +554,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C29"/>
     </row>
@@ -560,7 +563,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C30"/>
     </row>
@@ -569,7 +572,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C31"/>
     </row>
@@ -578,7 +581,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C32"/>
     </row>
@@ -587,7 +590,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C33"/>
     </row>
@@ -596,7 +599,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C34"/>
     </row>
@@ -605,7 +608,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C35"/>
     </row>
@@ -614,7 +617,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C36"/>
     </row>
@@ -623,7 +626,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C37"/>
     </row>
@@ -632,7 +635,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C38"/>
     </row>
@@ -641,7 +644,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C39"/>
     </row>
@@ -650,7 +653,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C40"/>
     </row>
@@ -659,7 +662,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C41"/>
     </row>
@@ -668,7 +671,7 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C42"/>
     </row>
@@ -677,7 +680,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C43"/>
     </row>
@@ -686,7 +689,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C44"/>
     </row>
@@ -695,7 +698,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C45"/>
     </row>
@@ -704,7 +707,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46"/>
     </row>
@@ -713,7 +716,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47"/>
     </row>
@@ -722,7 +725,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C48"/>
     </row>
@@ -740,7 +743,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C50"/>
     </row>
@@ -749,9 +752,18 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/SpawnList.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/SpawnList.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="76">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -29,157 +29,160 @@
     <t xml:space="preserve">all</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_statue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_guest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_animal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_neutral_war</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_readFail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_wilds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_dungeon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_dungeon_forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_randomFish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_human</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_undead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_pawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dungeon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">container_general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_generalExotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_weapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_gun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_healer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_furniture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_drink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_fruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_seeker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_booze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_meat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_bread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_sweet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_fish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_junk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_souvenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_drug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_blackmarket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_lamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">darksoup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wreck_junk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 11.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_statue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_guest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_animal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_neutral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_neutral_war</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_readFail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_wilds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_dungeon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_dungeon_forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_randomFish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_human</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_undead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_pawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dungeon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">container_general</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_general</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_generalExotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_weapon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_gun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_healer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_furniture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_drink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_fruit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_seeker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_booze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_meat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_bread</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_sweet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_fish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_junk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_souvenir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_drug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_blackmarket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_lamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">darksoup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wreck_junk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 21.0</t>
@@ -338,7 +341,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C5"/>
     </row>
@@ -347,7 +350,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6"/>
     </row>
@@ -356,7 +359,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7"/>
     </row>
@@ -365,7 +368,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8"/>
     </row>
@@ -374,7 +377,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9"/>
     </row>
@@ -383,7 +386,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10"/>
     </row>
@@ -392,7 +395,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11"/>
     </row>
@@ -401,7 +404,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12"/>
     </row>
@@ -410,7 +413,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13"/>
     </row>
@@ -419,7 +422,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14"/>
     </row>
@@ -428,7 +431,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15"/>
     </row>
@@ -437,7 +440,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16"/>
     </row>
@@ -446,7 +449,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17"/>
     </row>
@@ -455,7 +458,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18"/>
     </row>
@@ -464,7 +467,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19"/>
     </row>
@@ -473,7 +476,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20"/>
     </row>
@@ -482,7 +485,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21"/>
     </row>
@@ -491,7 +494,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22"/>
     </row>
@@ -500,7 +503,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23"/>
     </row>
@@ -518,7 +521,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25"/>
     </row>
@@ -563,7 +566,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30"/>
     </row>
@@ -581,7 +584,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C32"/>
     </row>
@@ -599,7 +602,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C34"/>
     </row>
@@ -644,7 +647,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39"/>
     </row>
@@ -680,7 +683,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43"/>
     </row>
@@ -734,7 +737,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C49"/>
     </row>
@@ -743,7 +746,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C50"/>
     </row>
@@ -752,7 +755,7 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C51"/>
     </row>
@@ -761,7 +764,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C52"/>
     </row>
